--- a/Utility Apps/animes.xlsx
+++ b/Utility Apps/animes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bibliotecas\Others\GitHub\choukpop-games-saves\Utility Apps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0C43AF-40FC-41D7-AF61-6D0D675D1750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B971B783-A3C4-4E59-8AFC-C1FA12C4A4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="816" xr2:uid="{57D189D9-1594-4AFF-BB28-71E87BC65B2F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="816" activeTab="6" xr2:uid="{57D189D9-1594-4AFF-BB28-71E87BC65B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Doramas" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="1216">
   <si>
     <t>Japan Name</t>
   </si>
@@ -3678,6 +3678,18 @@
   </si>
   <si>
     <t>https://myanimelist.net/anime/64441/Kanan-sama_wa_Akumade_Choroi_2nd_Season</t>
+  </si>
+  <si>
+    <t>Shinja Zero no Megami-sama to Hajimeru Isekai Kouryaku</t>
+  </si>
+  <si>
+    <t>Full Clearing Another World under a Goddess with Zero Believers</t>
+  </si>
+  <si>
+    <t>Tsuihou sareta Cheat Fuyo Majutsushi wa Kimama na Second Life wo Ouka suru. Ore wa Buki dake ja Naku, Arayuru Mono ni "Kyouka Point" wo Fuyo Dekiru shi, Ore no Ishi de Itsudemo Kouka wo Kaijo Dekiru kedo, Nokotta Hitotachi Daijoubu?</t>
+  </si>
+  <si>
+    <t>The Laid-Off Cheat-Granting Mage Enjoys a Second Lease on Life</t>
   </si>
 </sst>
 </file>
@@ -3867,7 +3879,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3898,7 +3910,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3912,6 +3924,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3945,12 +3960,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4306,11 +4315,11 @@
       <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
       <c r="G2"/>
     </row>
     <row r="3" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
@@ -4335,7 +4344,7 @@
       <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G4"/>
@@ -4350,7 +4359,7 @@
       <c r="E5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G5"/>
@@ -4365,7 +4374,7 @@
       <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G6"/>
@@ -4380,7 +4389,7 @@
       <c r="E7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="17" t="s">
         <v>25</v>
       </c>
       <c r="G7"/>
@@ -4395,7 +4404,7 @@
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="17" t="s">
         <v>28</v>
       </c>
       <c r="G8"/>
@@ -4407,7 +4416,7 @@
       <c r="E9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="17" t="s">
         <v>30</v>
       </c>
       <c r="G9"/>
@@ -4419,7 +4428,7 @@
       <c r="E10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="17" t="s">
         <v>37</v>
       </c>
       <c r="G10"/>
@@ -4431,7 +4440,7 @@
       <c r="E11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G11"/>
@@ -4439,7 +4448,7 @@
     <row r="12" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="29"/>
+      <c r="F12" s="17"/>
       <c r="G12"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -4533,34 +4542,34 @@
       <c r="G2"/>
     </row>
     <row r="3" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>731</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="24"/>
       <c r="F3" s="10" t="s">
         <v>731</v>
       </c>
       <c r="G3" s="14"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
       <c r="F4" s="10" t="s">
         <v>732</v>
       </c>
       <c r="G4" s="14"/>
     </row>
     <row r="5" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="10" t="s">
         <v>733</v>
       </c>
       <c r="G5" s="14"/>
     </row>
     <row r="6" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6" s="10" t="s">
         <v>734</v>
       </c>
@@ -4603,10 +4612,10 @@
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="24" t="s">
         <v>741</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="24" t="s">
         <v>742</v>
       </c>
       <c r="F10" s="10" t="s">
@@ -4615,18 +4624,18 @@
       <c r="G10" s="14"/>
     </row>
     <row r="11" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="10" t="s">
         <v>743</v>
       </c>
       <c r="G11" s="14"/>
     </row>
     <row r="12" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="24" t="s">
         <v>744</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="24" t="s">
         <v>745</v>
       </c>
       <c r="F12" s="10" t="s">
@@ -4635,8 +4644,8 @@
       <c r="G12" s="14"/>
     </row>
     <row r="13" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="10" t="s">
         <v>746</v>
       </c>
@@ -4655,10 +4664,10 @@
       <c r="G14" s="14"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="24" t="s">
         <v>749</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="24" t="s">
         <v>750</v>
       </c>
       <c r="F15" s="10" t="s">
@@ -4667,18 +4676,18 @@
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="10" t="s">
         <v>751</v>
       </c>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="24" t="s">
         <v>752</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="24" t="s">
         <v>753</v>
       </c>
       <c r="F17" s="10" t="s">
@@ -4687,8 +4696,8 @@
       <c r="G17" s="14"/>
     </row>
     <row r="18" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="10" t="s">
         <v>754</v>
       </c>
@@ -4717,34 +4726,34 @@
       <c r="G20" s="14"/>
     </row>
     <row r="21" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="24" t="s">
         <v>758</v>
       </c>
-      <c r="E21" s="23"/>
+      <c r="E21" s="24"/>
       <c r="F21" s="10" t="s">
         <v>759</v>
       </c>
       <c r="G21" s="14"/>
     </row>
     <row r="22" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
       <c r="F22" s="10" t="s">
         <v>760</v>
       </c>
       <c r="G22" s="14"/>
     </row>
     <row r="23" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="10" t="s">
         <v>761</v>
       </c>
       <c r="G23" s="14"/>
     </row>
     <row r="24" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
       <c r="F24" s="10" t="s">
         <v>762</v>
       </c>
@@ -4763,10 +4772,10 @@
       <c r="G25" s="14"/>
     </row>
     <row r="26" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="24" t="s">
         <v>765</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="24" t="s">
         <v>766</v>
       </c>
       <c r="F26" s="10" t="s">
@@ -4775,42 +4784,42 @@
       <c r="G26" s="14"/>
     </row>
     <row r="27" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
       <c r="F27" s="10" t="s">
         <v>768</v>
       </c>
       <c r="G27" s="14"/>
     </row>
     <row r="28" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="10" t="s">
         <v>769</v>
       </c>
       <c r="G28" s="14"/>
     </row>
     <row r="29" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
       <c r="F29" s="10" t="s">
         <v>770</v>
       </c>
       <c r="G29" s="14"/>
     </row>
     <row r="30" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="10" t="s">
         <v>771</v>
       </c>
       <c r="G30" s="14"/>
     </row>
     <row r="31" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="24" t="s">
         <v>772</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="24" t="s">
         <v>773</v>
       </c>
       <c r="F31" s="10" t="s">
@@ -4819,8 +4828,8 @@
       <c r="G31" s="14"/>
     </row>
     <row r="32" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="10" t="s">
         <v>775</v>
       </c>
@@ -4839,10 +4848,10 @@
       <c r="G33" s="14"/>
     </row>
     <row r="34" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="24" t="s">
         <v>778</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="E34" s="24" t="s">
         <v>779</v>
       </c>
       <c r="F34" s="10" t="s">
@@ -4851,24 +4860,24 @@
       <c r="G34" s="14"/>
     </row>
     <row r="35" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
       <c r="F35" s="10" t="s">
         <v>780</v>
       </c>
       <c r="G35" s="14"/>
     </row>
     <row r="36" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="10" t="s">
         <v>781</v>
       </c>
       <c r="G36" s="14"/>
     </row>
     <row r="37" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
       <c r="F37" s="10" t="s">
         <v>782</v>
       </c>
@@ -4899,10 +4908,10 @@
       <c r="G39" s="14"/>
     </row>
     <row r="40" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="23" t="s">
+      <c r="D40" s="24" t="s">
         <v>787</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="E40" s="24" t="s">
         <v>788</v>
       </c>
       <c r="F40" s="10" t="s">
@@ -4911,34 +4920,34 @@
       <c r="G40" s="14"/>
     </row>
     <row r="41" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
       <c r="F41" s="10" t="s">
         <v>790</v>
       </c>
       <c r="G41" s="14"/>
     </row>
     <row r="42" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
       <c r="F42" s="10" t="s">
         <v>791</v>
       </c>
       <c r="G42" s="14"/>
     </row>
     <row r="43" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
       <c r="F43" s="10" t="s">
         <v>792</v>
       </c>
       <c r="G43" s="14"/>
     </row>
     <row r="44" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D44" s="23" t="s">
+      <c r="D44" s="24" t="s">
         <v>793</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="24" t="s">
         <v>794</v>
       </c>
       <c r="F44" s="10" t="s">
@@ -4947,8 +4956,8 @@
       <c r="G44" s="14"/>
     </row>
     <row r="45" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
       <c r="F45" s="10" t="s">
         <v>795</v>
       </c>
@@ -4967,10 +4976,10 @@
       <c r="G46" s="14"/>
     </row>
     <row r="47" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="21" t="s">
         <v>798</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="21" t="s">
         <v>799</v>
       </c>
       <c r="F47" s="10" t="s">
@@ -4979,32 +4988,32 @@
       <c r="G47" s="14"/>
     </row>
     <row r="48" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
       <c r="F48" s="10" t="s">
         <v>800</v>
       </c>
       <c r="G48" s="14"/>
     </row>
     <row r="49" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
       <c r="F49" s="10" t="s">
         <v>801</v>
       </c>
       <c r="G49" s="14"/>
     </row>
     <row r="50" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
       <c r="F50" s="10" t="s">
         <v>802</v>
       </c>
       <c r="G50" s="14"/>
     </row>
     <row r="51" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
       <c r="F51" s="10" t="s">
         <v>1181</v>
       </c>
@@ -5035,10 +5044,10 @@
       <c r="G53" s="14"/>
     </row>
     <row r="54" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="24" t="s">
         <v>807</v>
       </c>
-      <c r="E54" s="23" t="s">
+      <c r="E54" s="24" t="s">
         <v>808</v>
       </c>
       <c r="F54" s="10" t="s">
@@ -5047,8 +5056,8 @@
       <c r="G54" s="14"/>
     </row>
     <row r="55" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
       <c r="F55" s="10" t="s">
         <v>809</v>
       </c>
@@ -5067,36 +5076,36 @@
       <c r="G56" s="14"/>
     </row>
     <row r="57" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="24" t="s">
         <v>812</v>
       </c>
-      <c r="E57" s="23"/>
+      <c r="E57" s="24"/>
       <c r="F57" s="10" t="s">
         <v>812</v>
       </c>
       <c r="G57" s="14"/>
     </row>
     <row r="58" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
       <c r="F58" s="10" t="s">
         <v>813</v>
       </c>
       <c r="G58" s="14"/>
     </row>
     <row r="59" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D59" s="23" t="s">
+      <c r="D59" s="24" t="s">
         <v>814</v>
       </c>
-      <c r="E59" s="23"/>
+      <c r="E59" s="24"/>
       <c r="F59" s="10" t="s">
         <v>815</v>
       </c>
       <c r="G59" s="14"/>
     </row>
     <row r="60" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
       <c r="F60" s="10" t="s">
         <v>816</v>
       </c>
@@ -5255,18 +5264,18 @@
       <c r="G73" s="14"/>
     </row>
     <row r="74" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="23" t="s">
+      <c r="D74" s="24" t="s">
         <v>841</v>
       </c>
-      <c r="E74" s="23"/>
+      <c r="E74" s="24"/>
       <c r="F74" s="10" t="s">
         <v>841</v>
       </c>
       <c r="G74" s="14"/>
     </row>
     <row r="75" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
       <c r="F75" s="10" t="s">
         <v>842</v>
       </c>
@@ -5307,10 +5316,10 @@
       <c r="G78" s="14"/>
     </row>
     <row r="79" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D79" s="23" t="s">
+      <c r="D79" s="24" t="s">
         <v>848</v>
       </c>
-      <c r="E79" s="23" t="s">
+      <c r="E79" s="24" t="s">
         <v>849</v>
       </c>
       <c r="F79" s="10" t="s">
@@ -5319,18 +5328,18 @@
       <c r="G79" s="14"/>
     </row>
     <row r="80" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
       <c r="F80" s="10" t="s">
         <v>850</v>
       </c>
       <c r="G80" s="14"/>
     </row>
     <row r="81" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D81" s="23" t="s">
+      <c r="D81" s="24" t="s">
         <v>851</v>
       </c>
-      <c r="E81" s="23" t="s">
+      <c r="E81" s="24" t="s">
         <v>852</v>
       </c>
       <c r="F81" s="10" t="s">
@@ -5339,8 +5348,8 @@
       <c r="G81" s="14"/>
     </row>
     <row r="82" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
+      <c r="D82" s="24"/>
+      <c r="E82" s="24"/>
       <c r="F82" s="10" t="s">
         <v>853</v>
       </c>
@@ -5441,10 +5450,10 @@
       <c r="G90" s="14"/>
     </row>
     <row r="91" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D91" s="23" t="s">
+      <c r="D91" s="24" t="s">
         <v>869</v>
       </c>
-      <c r="E91" s="23" t="s">
+      <c r="E91" s="24" t="s">
         <v>870</v>
       </c>
       <c r="F91" s="10" t="s">
@@ -5453,8 +5462,8 @@
       <c r="G91" s="14"/>
     </row>
     <row r="92" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D92" s="23"/>
-      <c r="E92" s="23"/>
+      <c r="D92" s="24"/>
+      <c r="E92" s="24"/>
       <c r="F92" s="10" t="s">
         <v>871</v>
       </c>
@@ -5543,10 +5552,10 @@
       <c r="G99" s="14"/>
     </row>
     <row r="100" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="23" t="s">
+      <c r="D100" s="24" t="s">
         <v>885</v>
       </c>
-      <c r="E100" s="23" t="s">
+      <c r="E100" s="24" t="s">
         <v>886</v>
       </c>
       <c r="F100" s="10" t="s">
@@ -5555,18 +5564,18 @@
       <c r="G100" s="14"/>
     </row>
     <row r="101" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D101" s="23"/>
-      <c r="E101" s="23"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
       <c r="F101" s="10" t="s">
         <v>887</v>
       </c>
       <c r="G101" s="14"/>
     </row>
     <row r="102" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D102" s="23" t="s">
+      <c r="D102" s="24" t="s">
         <v>888</v>
       </c>
-      <c r="E102" s="23" t="s">
+      <c r="E102" s="24" t="s">
         <v>889</v>
       </c>
       <c r="F102" s="10" t="s">
@@ -5575,8 +5584,8 @@
       <c r="G102" s="14"/>
     </row>
     <row r="103" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D103" s="23"/>
-      <c r="E103" s="23"/>
+      <c r="D103" s="24"/>
+      <c r="E103" s="24"/>
       <c r="F103" s="10" t="s">
         <v>890</v>
       </c>
@@ -5605,10 +5614,10 @@
       <c r="G105" s="14"/>
     </row>
     <row r="106" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D106" s="23" t="s">
+      <c r="D106" s="24" t="s">
         <v>894</v>
       </c>
-      <c r="E106" s="23" t="s">
+      <c r="E106" s="24" t="s">
         <v>895</v>
       </c>
       <c r="F106" s="10" t="s">
@@ -5617,8 +5626,8 @@
       <c r="G106" s="14"/>
     </row>
     <row r="107" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D107" s="23"/>
-      <c r="E107" s="23"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
       <c r="F107" s="10" t="s">
         <v>896</v>
       </c>
@@ -5671,18 +5680,18 @@
       <c r="G111" s="14"/>
     </row>
     <row r="112" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D112" s="23" t="s">
+      <c r="D112" s="24" t="s">
         <v>904</v>
       </c>
-      <c r="E112" s="23"/>
+      <c r="E112" s="24"/>
       <c r="F112" s="10" t="s">
         <v>904</v>
       </c>
       <c r="G112" s="14"/>
     </row>
     <row r="113" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D113" s="23"/>
-      <c r="E113" s="23"/>
+      <c r="D113" s="24"/>
+      <c r="E113" s="24"/>
       <c r="F113" s="10" t="s">
         <v>905</v>
       </c>
@@ -5775,10 +5784,10 @@
       <c r="G121" s="14"/>
     </row>
     <row r="122" spans="4:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D122" s="20" t="s">
+      <c r="D122" s="21" t="s">
         <v>917</v>
       </c>
-      <c r="E122" s="20" t="s">
+      <c r="E122" s="21" t="s">
         <v>918</v>
       </c>
       <c r="F122" s="10" t="s">
@@ -5787,16 +5796,16 @@
       <c r="G122" s="14"/>
     </row>
     <row r="123" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D123" s="22"/>
-      <c r="E123" s="22"/>
+      <c r="D123" s="23"/>
+      <c r="E123" s="23"/>
       <c r="F123" s="10" t="s">
         <v>919</v>
       </c>
       <c r="G123" s="14"/>
     </row>
     <row r="124" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D124" s="21"/>
-      <c r="E124" s="21"/>
+      <c r="D124" s="22"/>
+      <c r="E124" s="22"/>
       <c r="F124" s="10" t="s">
         <v>1133</v>
       </c>
@@ -5907,26 +5916,26 @@
       <c r="G133" s="14"/>
     </row>
     <row r="134" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D134" s="23" t="s">
+      <c r="D134" s="24" t="s">
         <v>936</v>
       </c>
-      <c r="E134" s="23"/>
+      <c r="E134" s="24"/>
       <c r="F134" s="10" t="s">
         <v>937</v>
       </c>
       <c r="G134" s="14"/>
     </row>
     <row r="135" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D135" s="23"/>
-      <c r="E135" s="23"/>
+      <c r="D135" s="24"/>
+      <c r="E135" s="24"/>
       <c r="F135" s="10" t="s">
         <v>938</v>
       </c>
       <c r="G135" s="14"/>
     </row>
     <row r="136" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D136" s="23"/>
-      <c r="E136" s="23"/>
+      <c r="D136" s="24"/>
+      <c r="E136" s="24"/>
       <c r="F136" s="10" t="s">
         <v>939</v>
       </c>
@@ -6173,10 +6182,10 @@
       <c r="G157" s="14"/>
     </row>
     <row r="158" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D158" s="23" t="s">
+      <c r="D158" s="24" t="s">
         <v>976</v>
       </c>
-      <c r="E158" s="23" t="s">
+      <c r="E158" s="24" t="s">
         <v>977</v>
       </c>
       <c r="F158" s="10" t="s">
@@ -6185,32 +6194,32 @@
       <c r="G158" s="14"/>
     </row>
     <row r="159" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D159" s="23"/>
-      <c r="E159" s="23"/>
+      <c r="D159" s="24"/>
+      <c r="E159" s="24"/>
       <c r="F159" s="10" t="s">
         <v>978</v>
       </c>
       <c r="G159" s="14"/>
     </row>
     <row r="160" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D160" s="23"/>
-      <c r="E160" s="23"/>
+      <c r="D160" s="24"/>
+      <c r="E160" s="24"/>
       <c r="F160" s="10" t="s">
         <v>979</v>
       </c>
       <c r="G160" s="14"/>
     </row>
     <row r="161" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D161" s="23"/>
-      <c r="E161" s="23"/>
+      <c r="D161" s="24"/>
+      <c r="E161" s="24"/>
       <c r="F161" s="10" t="s">
         <v>980</v>
       </c>
       <c r="G161" s="14"/>
     </row>
     <row r="162" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D162" s="23"/>
-      <c r="E162" s="23"/>
+      <c r="D162" s="24"/>
+      <c r="E162" s="24"/>
       <c r="F162" s="10" t="s">
         <v>981</v>
       </c>
@@ -6249,28 +6258,28 @@
       <c r="G165" s="14"/>
     </row>
     <row r="166" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D166" s="20" t="s">
+      <c r="D166" s="21" t="s">
         <v>986</v>
       </c>
-      <c r="E166" s="20"/>
+      <c r="E166" s="21"/>
       <c r="F166" s="10" t="s">
         <v>986</v>
       </c>
       <c r="G166" s="14"/>
     </row>
     <row r="167" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D167" s="21"/>
-      <c r="E167" s="21"/>
+      <c r="D167" s="22"/>
+      <c r="E167" s="22"/>
       <c r="F167" s="10" t="s">
         <v>987</v>
       </c>
       <c r="G167" s="14"/>
     </row>
     <row r="168" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D168" s="20" t="s">
+      <c r="D168" s="21" t="s">
         <v>988</v>
       </c>
-      <c r="E168" s="20" t="s">
+      <c r="E168" s="21" t="s">
         <v>989</v>
       </c>
       <c r="F168" s="10" t="s">
@@ -6279,8 +6288,8 @@
       <c r="G168" s="14"/>
     </row>
     <row r="169" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D169" s="21"/>
-      <c r="E169" s="21"/>
+      <c r="D169" s="22"/>
+      <c r="E169" s="22"/>
       <c r="F169" s="10" t="s">
         <v>990</v>
       </c>
@@ -6363,10 +6372,10 @@
       <c r="G176" s="14"/>
     </row>
     <row r="177" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D177" s="20" t="s">
+      <c r="D177" s="21" t="s">
         <v>1001</v>
       </c>
-      <c r="E177" s="20" t="s">
+      <c r="E177" s="21" t="s">
         <v>1002</v>
       </c>
       <c r="F177" s="10" t="s">
@@ -6375,36 +6384,36 @@
       <c r="G177" s="14"/>
     </row>
     <row r="178" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D178" s="21"/>
-      <c r="E178" s="21"/>
+      <c r="D178" s="22"/>
+      <c r="E178" s="22"/>
       <c r="F178" s="10" t="s">
         <v>1003</v>
       </c>
       <c r="G178" s="14"/>
     </row>
     <row r="179" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D179" s="20" t="s">
+      <c r="D179" s="21" t="s">
         <v>1004</v>
       </c>
-      <c r="E179" s="20"/>
+      <c r="E179" s="21"/>
       <c r="F179" s="10" t="s">
         <v>1004</v>
       </c>
       <c r="G179" s="14"/>
     </row>
     <row r="180" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D180" s="21"/>
-      <c r="E180" s="21"/>
+      <c r="D180" s="22"/>
+      <c r="E180" s="22"/>
       <c r="F180" s="10" t="s">
         <v>1005</v>
       </c>
       <c r="G180" s="14"/>
     </row>
     <row r="181" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D181" s="20" t="s">
+      <c r="D181" s="21" t="s">
         <v>1006</v>
       </c>
-      <c r="E181" s="20" t="s">
+      <c r="E181" s="21" t="s">
         <v>1007</v>
       </c>
       <c r="F181" s="10" t="s">
@@ -6413,8 +6422,8 @@
       <c r="G181" s="14"/>
     </row>
     <row r="182" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D182" s="21"/>
-      <c r="E182" s="21"/>
+      <c r="D182" s="22"/>
+      <c r="E182" s="22"/>
       <c r="F182" s="10" t="s">
         <v>1008</v>
       </c>
@@ -6465,10 +6474,10 @@
       <c r="G186" s="14"/>
     </row>
     <row r="187" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D187" s="20" t="s">
+      <c r="D187" s="21" t="s">
         <v>1015</v>
       </c>
-      <c r="E187" s="20" t="s">
+      <c r="E187" s="21" t="s">
         <v>1016</v>
       </c>
       <c r="F187" s="10" t="s">
@@ -6477,24 +6486,24 @@
       <c r="G187" s="14"/>
     </row>
     <row r="188" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D188" s="22"/>
-      <c r="E188" s="22"/>
+      <c r="D188" s="23"/>
+      <c r="E188" s="23"/>
       <c r="F188" s="10" t="s">
         <v>1017</v>
       </c>
       <c r="G188" s="14"/>
     </row>
     <row r="189" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D189" s="22"/>
-      <c r="E189" s="22"/>
+      <c r="D189" s="23"/>
+      <c r="E189" s="23"/>
       <c r="F189" s="10" t="s">
         <v>1018</v>
       </c>
       <c r="G189" s="14"/>
     </row>
     <row r="190" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D190" s="21"/>
-      <c r="E190" s="21"/>
+      <c r="D190" s="22"/>
+      <c r="E190" s="22"/>
       <c r="F190" s="10" t="s">
         <v>1019</v>
       </c>
@@ -6601,10 +6610,10 @@
       <c r="G199" s="14"/>
     </row>
     <row r="200" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D200" s="20" t="s">
+      <c r="D200" s="21" t="s">
         <v>1034</v>
       </c>
-      <c r="E200" s="20" t="s">
+      <c r="E200" s="21" t="s">
         <v>1035</v>
       </c>
       <c r="F200" s="10" t="s">
@@ -6613,18 +6622,18 @@
       <c r="G200" s="14"/>
     </row>
     <row r="201" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D201" s="21"/>
-      <c r="E201" s="21"/>
+      <c r="D201" s="22"/>
+      <c r="E201" s="22"/>
       <c r="F201" s="10" t="s">
         <v>1094</v>
       </c>
       <c r="G201" s="14"/>
     </row>
     <row r="202" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D202" s="20" t="s">
+      <c r="D202" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E202" s="20" t="s">
+      <c r="E202" s="21" t="s">
         <v>51</v>
       </c>
       <c r="F202" s="10" t="s">
@@ -6633,8 +6642,8 @@
       <c r="G202" s="14"/>
     </row>
     <row r="203" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D203" s="21"/>
-      <c r="E203" s="21"/>
+      <c r="D203" s="22"/>
+      <c r="E203" s="22"/>
       <c r="F203" s="10" t="s">
         <v>1129</v>
       </c>
@@ -6711,10 +6720,10 @@
       <c r="G209" s="14"/>
     </row>
     <row r="210" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D210" s="20" t="s">
+      <c r="D210" s="21" t="s">
         <v>1047</v>
       </c>
-      <c r="E210" s="20" t="s">
+      <c r="E210" s="21" t="s">
         <v>1048</v>
       </c>
       <c r="F210" s="10" t="s">
@@ -6723,8 +6732,8 @@
       <c r="G210" s="14"/>
     </row>
     <row r="211" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D211" s="21"/>
-      <c r="E211" s="21"/>
+      <c r="D211" s="22"/>
+      <c r="E211" s="22"/>
       <c r="F211" s="10" t="s">
         <v>1049</v>
       </c>
@@ -7056,7 +7065,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABABA4B8-1530-4AF1-931C-B7844404DE0A}">
-  <dimension ref="B1:G271"/>
+  <dimension ref="B1:G272"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="8"/>
@@ -7070,8 +7079,8 @@
     <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="str">
-        <f>CONCATENATE("Total: ",COUNTA(D3:D267))</f>
-        <v>Total: 168</v>
+        <f>CONCATENATE("Total: ",COUNTA(D3:D269))</f>
+        <v>Total: 170</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>0</v>
@@ -7085,10 +7094,10 @@
       <c r="G2"/>
     </row>
     <row r="3" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>382</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="28" t="s">
         <v>383</v>
       </c>
       <c r="F3" s="11" t="s">
@@ -7097,32 +7106,32 @@
       <c r="G3" s="14"/>
     </row>
     <row r="4" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
       <c r="F4" s="11" t="s">
         <v>385</v>
       </c>
       <c r="G4" s="14"/>
     </row>
     <row r="5" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="11" t="s">
         <v>386</v>
       </c>
       <c r="G5" s="14"/>
     </row>
     <row r="6" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="11" t="s">
         <v>387</v>
       </c>
       <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="11" t="s">
         <v>388</v>
       </c>
@@ -7141,10 +7150,10 @@
       <c r="G8" s="14"/>
     </row>
     <row r="9" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="28" t="s">
         <v>391</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="28" t="s">
         <v>392</v>
       </c>
       <c r="F9" s="11" t="s">
@@ -7153,18 +7162,18 @@
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="11" t="s">
         <v>393</v>
       </c>
       <c r="G10" s="14"/>
     </row>
     <row r="11" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="25" t="s">
         <v>49</v>
       </c>
       <c r="F11" s="11" t="s">
@@ -7173,42 +7182,42 @@
       <c r="G11" s="14"/>
     </row>
     <row r="12" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
       <c r="F12" s="11" t="s">
         <v>395</v>
       </c>
       <c r="G12" s="14"/>
     </row>
     <row r="13" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
       <c r="F13" s="11" t="s">
         <v>396</v>
       </c>
       <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="11" t="s">
         <v>397</v>
       </c>
       <c r="G14" s="14"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="11" t="s">
         <v>1160</v>
       </c>
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="2:7" ht="57" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="28" t="s">
         <v>398</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="28" t="s">
         <v>399</v>
       </c>
       <c r="F16" s="11" t="s">
@@ -7217,16 +7226,16 @@
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="4:7" ht="57" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
       <c r="F17" s="11" t="s">
         <v>400</v>
       </c>
       <c r="G17" s="14"/>
     </row>
     <row r="18" spans="4:7" ht="57" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
       <c r="F18" s="11" t="s">
         <v>401</v>
       </c>
@@ -7245,10 +7254,10 @@
       <c r="G19" s="14"/>
     </row>
     <row r="20" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="28" t="s">
         <v>404</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="28" t="s">
         <v>405</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -7257,60 +7266,60 @@
       <c r="G20" s="14"/>
     </row>
     <row r="21" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
       <c r="F21" s="11" t="s">
         <v>406</v>
       </c>
       <c r="G21" s="14"/>
     </row>
     <row r="22" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="28" t="s">
         <v>407</v>
       </c>
-      <c r="E22" s="27"/>
+      <c r="E22" s="28"/>
       <c r="F22" s="11" t="s">
         <v>407</v>
       </c>
       <c r="G22" s="14"/>
     </row>
     <row r="23" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
       <c r="F23" s="11" t="s">
         <v>408</v>
       </c>
       <c r="G23" s="14"/>
     </row>
     <row r="24" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
       <c r="F24" s="11" t="s">
         <v>409</v>
       </c>
       <c r="G24" s="14"/>
     </row>
     <row r="25" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
       <c r="F25" s="11" t="s">
         <v>410</v>
       </c>
       <c r="G25" s="14"/>
     </row>
     <row r="26" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
       <c r="F26" s="11" t="s">
         <v>411</v>
       </c>
       <c r="G26" s="14"/>
     </row>
     <row r="27" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="28" t="s">
         <v>412</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="28" t="s">
         <v>413</v>
       </c>
       <c r="F27" s="11" t="s">
@@ -7319,40 +7328,40 @@
       <c r="G27" s="14"/>
     </row>
     <row r="28" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
       <c r="F28" s="11" t="s">
         <v>415</v>
       </c>
       <c r="G28" s="14"/>
     </row>
     <row r="29" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
       <c r="F29" s="11" t="s">
         <v>416</v>
       </c>
       <c r="G29" s="14"/>
     </row>
     <row r="30" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
       <c r="F30" s="11" t="s">
         <v>417</v>
       </c>
       <c r="G30" s="14"/>
     </row>
     <row r="31" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
       <c r="F31" s="11" t="s">
         <v>418</v>
       </c>
       <c r="G31" s="14"/>
     </row>
     <row r="32" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
       <c r="F32" s="11" t="s">
         <v>419</v>
       </c>
@@ -7371,10 +7380,10 @@
       <c r="G33" s="14"/>
     </row>
     <row r="34" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="28" t="s">
         <v>422</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="28" t="s">
         <v>423</v>
       </c>
       <c r="F34" s="11" t="s">
@@ -7383,8 +7392,8 @@
       <c r="G34" s="14"/>
     </row>
     <row r="35" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
       <c r="F35" s="11" t="s">
         <v>424</v>
       </c>
@@ -7415,10 +7424,10 @@
       <c r="G37" s="14"/>
     </row>
     <row r="38" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="28" t="s">
         <v>429</v>
       </c>
-      <c r="E38" s="27" t="s">
+      <c r="E38" s="28" t="s">
         <v>430</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -7427,8 +7436,8 @@
       <c r="G38" s="14"/>
     </row>
     <row r="39" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
       <c r="F39" s="11" t="s">
         <v>431</v>
       </c>
@@ -7459,10 +7468,10 @@
       <c r="G41" s="14"/>
     </row>
     <row r="42" spans="4:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="25" t="s">
         <v>9</v>
       </c>
       <c r="F42" s="11" t="s">
@@ -7471,18 +7480,18 @@
       <c r="G42" s="14"/>
     </row>
     <row r="43" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
       <c r="F43" s="11" t="s">
         <v>1186</v>
       </c>
       <c r="G43" s="14"/>
     </row>
     <row r="44" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D44" s="27" t="s">
+      <c r="D44" s="28" t="s">
         <v>436</v>
       </c>
-      <c r="E44" s="27" t="s">
+      <c r="E44" s="28" t="s">
         <v>437</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -7491,8 +7500,8 @@
       <c r="G44" s="14"/>
     </row>
     <row r="45" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
       <c r="F45" s="11" t="s">
         <v>438</v>
       </c>
@@ -7511,10 +7520,10 @@
       <c r="G46" s="14"/>
     </row>
     <row r="47" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="28" t="s">
         <v>441</v>
       </c>
-      <c r="E47" s="27" t="s">
+      <c r="E47" s="28" t="s">
         <v>442</v>
       </c>
       <c r="F47" s="11" t="s">
@@ -7523,8 +7532,8 @@
       <c r="G47" s="14"/>
     </row>
     <row r="48" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
       <c r="F48" s="11" t="s">
         <v>443</v>
       </c>
@@ -7541,60 +7550,60 @@
       <c r="G49" s="14"/>
     </row>
     <row r="50" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D50" s="27" t="s">
+      <c r="D50" s="28" t="s">
         <v>445</v>
       </c>
-      <c r="E50" s="27"/>
+      <c r="E50" s="28"/>
       <c r="F50" s="11" t="s">
         <v>445</v>
       </c>
       <c r="G50" s="14"/>
     </row>
     <row r="51" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
       <c r="F51" s="11" t="s">
         <v>446</v>
       </c>
       <c r="G51" s="14"/>
     </row>
     <row r="52" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
       <c r="F52" s="11" t="s">
         <v>447</v>
       </c>
       <c r="G52" s="14"/>
     </row>
     <row r="53" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="28" t="s">
         <v>448</v>
       </c>
-      <c r="E53" s="27"/>
+      <c r="E53" s="28"/>
       <c r="F53" s="11" t="s">
         <v>448</v>
       </c>
       <c r="G53" s="14"/>
     </row>
     <row r="54" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
       <c r="F54" s="11" t="s">
         <v>449</v>
       </c>
       <c r="G54" s="14"/>
     </row>
     <row r="55" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
       <c r="F55" s="11" t="s">
         <v>450</v>
       </c>
       <c r="G55" s="14"/>
     </row>
     <row r="56" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
       <c r="F56" s="11" t="s">
         <v>451</v>
       </c>
@@ -7633,10 +7642,10 @@
       <c r="G59" s="14"/>
     </row>
     <row r="60" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="E60" s="27" t="s">
+      <c r="E60" s="28" t="s">
         <v>457</v>
       </c>
       <c r="F60" s="11" t="s">
@@ -7645,8 +7654,8 @@
       <c r="G60" s="14"/>
     </row>
     <row r="61" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
       <c r="F61" s="11" t="s">
         <v>458</v>
       </c>
@@ -7675,10 +7684,10 @@
       <c r="G63" s="14"/>
     </row>
     <row r="64" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D64" s="27" t="s">
+      <c r="D64" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="E64" s="27" t="s">
+      <c r="E64" s="28" t="s">
         <v>463</v>
       </c>
       <c r="F64" s="11" t="s">
@@ -7687,34 +7696,34 @@
       <c r="G64" s="14"/>
     </row>
     <row r="65" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
       <c r="F65" s="11" t="s">
         <v>464</v>
       </c>
       <c r="G65" s="14"/>
     </row>
     <row r="66" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
       <c r="F66" s="11" t="s">
         <v>465</v>
       </c>
       <c r="G66" s="14"/>
     </row>
     <row r="67" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
       <c r="F67" s="11" t="s">
         <v>466</v>
       </c>
       <c r="G67" s="14"/>
     </row>
     <row r="68" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D68" s="27" t="s">
+      <c r="D68" s="28" t="s">
         <v>467</v>
       </c>
-      <c r="E68" s="27" t="s">
+      <c r="E68" s="28" t="s">
         <v>468</v>
       </c>
       <c r="F68" s="11" t="s">
@@ -7723,50 +7732,50 @@
       <c r="G68" s="14"/>
     </row>
     <row r="69" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
       <c r="F69" s="11" t="s">
         <v>469</v>
       </c>
       <c r="G69" s="14"/>
     </row>
     <row r="70" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
       <c r="F70" s="11" t="s">
         <v>470</v>
       </c>
       <c r="G70" s="14"/>
     </row>
     <row r="71" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
       <c r="F71" s="11" t="s">
         <v>471</v>
       </c>
       <c r="G71" s="14"/>
     </row>
     <row r="72" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
       <c r="F72" s="11" t="s">
         <v>472</v>
       </c>
       <c r="G72" s="14"/>
     </row>
     <row r="73" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
       <c r="F73" s="11" t="s">
         <v>473</v>
       </c>
       <c r="G73" s="14"/>
     </row>
     <row r="74" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="27" t="s">
+      <c r="D74" s="28" t="s">
         <v>474</v>
       </c>
-      <c r="E74" s="27" t="s">
+      <c r="E74" s="28" t="s">
         <v>475</v>
       </c>
       <c r="F74" s="11" t="s">
@@ -7775,8 +7784,8 @@
       <c r="G74" s="14"/>
     </row>
     <row r="75" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
       <c r="F75" s="11" t="s">
         <v>476</v>
       </c>
@@ -7795,10 +7804,10 @@
       <c r="G76" s="14"/>
     </row>
     <row r="77" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D77" s="27" t="s">
+      <c r="D77" s="28" t="s">
         <v>479</v>
       </c>
-      <c r="E77" s="27" t="s">
+      <c r="E77" s="28" t="s">
         <v>480</v>
       </c>
       <c r="F77" s="11" t="s">
@@ -7807,8 +7816,8 @@
       <c r="G77" s="14"/>
     </row>
     <row r="78" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
       <c r="F78" s="11" t="s">
         <v>481</v>
       </c>
@@ -7825,52 +7834,52 @@
       <c r="G79" s="14"/>
     </row>
     <row r="80" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D80" s="27" t="s">
+      <c r="D80" s="28" t="s">
         <v>483</v>
       </c>
-      <c r="E80" s="27"/>
+      <c r="E80" s="28"/>
       <c r="F80" s="11" t="s">
         <v>483</v>
       </c>
       <c r="G80" s="14"/>
     </row>
     <row r="81" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
       <c r="F81" s="11" t="s">
         <v>484</v>
       </c>
       <c r="G81" s="14"/>
     </row>
     <row r="82" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
+      <c r="D82" s="28"/>
+      <c r="E82" s="28"/>
       <c r="F82" s="11" t="s">
         <v>485</v>
       </c>
       <c r="G82" s="14"/>
     </row>
     <row r="83" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
+      <c r="D83" s="28"/>
+      <c r="E83" s="28"/>
       <c r="F83" s="11" t="s">
         <v>486</v>
       </c>
       <c r="G83" s="14"/>
     </row>
     <row r="84" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="28" t="s">
         <v>487</v>
       </c>
-      <c r="E84" s="27"/>
+      <c r="E84" s="28"/>
       <c r="F84" s="11" t="s">
         <v>487</v>
       </c>
       <c r="G84" s="14"/>
     </row>
     <row r="85" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
+      <c r="D85" s="28"/>
+      <c r="E85" s="28"/>
       <c r="F85" s="11" t="s">
         <v>488</v>
       </c>
@@ -7887,10 +7896,10 @@
       <c r="G86" s="14"/>
     </row>
     <row r="87" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D87" s="27" t="s">
+      <c r="D87" s="28" t="s">
         <v>490</v>
       </c>
-      <c r="E87" s="27" t="s">
+      <c r="E87" s="28" t="s">
         <v>491</v>
       </c>
       <c r="F87" s="11" t="s">
@@ -7899,50 +7908,50 @@
       <c r="G87" s="14"/>
     </row>
     <row r="88" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D88" s="27"/>
-      <c r="E88" s="27"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
       <c r="F88" s="11" t="s">
         <v>493</v>
       </c>
       <c r="G88" s="14"/>
     </row>
     <row r="89" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
       <c r="F89" s="11" t="s">
         <v>494</v>
       </c>
       <c r="G89" s="14"/>
     </row>
     <row r="90" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
       <c r="F90" s="11" t="s">
         <v>495</v>
       </c>
       <c r="G90" s="14"/>
     </row>
     <row r="91" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="28"/>
       <c r="F91" s="11" t="s">
         <v>496</v>
       </c>
       <c r="G91" s="14"/>
     </row>
     <row r="92" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D92" s="27"/>
-      <c r="E92" s="27"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
       <c r="F92" s="11" t="s">
         <v>497</v>
       </c>
       <c r="G92" s="14"/>
     </row>
     <row r="93" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D93" s="27" t="s">
+      <c r="D93" s="28" t="s">
         <v>498</v>
       </c>
-      <c r="E93" s="27" t="s">
+      <c r="E93" s="28" t="s">
         <v>499</v>
       </c>
       <c r="F93" s="11" t="s">
@@ -7951,34 +7960,34 @@
       <c r="G93" s="14"/>
     </row>
     <row r="94" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D94" s="27"/>
-      <c r="E94" s="27"/>
+      <c r="D94" s="28"/>
+      <c r="E94" s="28"/>
       <c r="F94" s="11" t="s">
         <v>501</v>
       </c>
       <c r="G94" s="14"/>
     </row>
     <row r="95" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D95" s="27"/>
-      <c r="E95" s="27"/>
+      <c r="D95" s="28"/>
+      <c r="E95" s="28"/>
       <c r="F95" s="11" t="s">
         <v>502</v>
       </c>
       <c r="G95" s="14"/>
     </row>
     <row r="96" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D96" s="27"/>
-      <c r="E96" s="27"/>
+      <c r="D96" s="28"/>
+      <c r="E96" s="28"/>
       <c r="F96" s="11" t="s">
         <v>503</v>
       </c>
       <c r="G96" s="14"/>
     </row>
     <row r="97" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D97" s="24" t="s">
+      <c r="D97" s="25" t="s">
         <v>504</v>
       </c>
-      <c r="E97" s="24" t="s">
+      <c r="E97" s="25" t="s">
         <v>505</v>
       </c>
       <c r="F97" s="11" t="s">
@@ -7987,92 +7996,92 @@
       <c r="G97" s="14"/>
     </row>
     <row r="98" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
       <c r="F98" s="11" t="s">
         <v>506</v>
       </c>
       <c r="G98" s="14"/>
     </row>
     <row r="99" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D99" s="26"/>
-      <c r="E99" s="26"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
       <c r="F99" s="11" t="s">
         <v>507</v>
       </c>
       <c r="G99" s="14"/>
     </row>
     <row r="100" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D100" s="25"/>
-      <c r="E100" s="25"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
       <c r="F100" s="11" t="s">
         <v>1162</v>
       </c>
       <c r="G100" s="14"/>
     </row>
     <row r="101" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D101" s="27" t="s">
+      <c r="D101" s="28" t="s">
         <v>508</v>
       </c>
-      <c r="E101" s="27"/>
+      <c r="E101" s="28"/>
       <c r="F101" s="11" t="s">
         <v>508</v>
       </c>
       <c r="G101" s="14"/>
     </row>
     <row r="102" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D102" s="27"/>
-      <c r="E102" s="27"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="28"/>
       <c r="F102" s="11" t="s">
         <v>509</v>
       </c>
       <c r="G102" s="14"/>
     </row>
     <row r="103" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D103" s="27"/>
-      <c r="E103" s="27"/>
+      <c r="D103" s="28"/>
+      <c r="E103" s="28"/>
       <c r="F103" s="11" t="s">
         <v>510</v>
       </c>
       <c r="G103" s="14"/>
     </row>
     <row r="104" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D104" s="27"/>
-      <c r="E104" s="27"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="28"/>
       <c r="F104" s="11" t="s">
         <v>511</v>
       </c>
       <c r="G104" s="14"/>
     </row>
     <row r="105" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D105" s="27"/>
-      <c r="E105" s="27"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="28"/>
       <c r="F105" s="11" t="s">
         <v>512</v>
       </c>
       <c r="G105" s="14"/>
     </row>
     <row r="106" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D106" s="27"/>
-      <c r="E106" s="27"/>
+      <c r="D106" s="28"/>
+      <c r="E106" s="28"/>
       <c r="F106" s="11" t="s">
         <v>513</v>
       </c>
       <c r="G106" s="14"/>
     </row>
     <row r="107" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D107" s="27"/>
-      <c r="E107" s="27"/>
+      <c r="D107" s="28"/>
+      <c r="E107" s="28"/>
       <c r="F107" s="11" t="s">
         <v>514</v>
       </c>
       <c r="G107" s="14"/>
     </row>
     <row r="108" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D108" s="27" t="s">
+      <c r="D108" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="E108" s="27" t="s">
+      <c r="E108" s="28" t="s">
         <v>516</v>
       </c>
       <c r="F108" s="11" t="s">
@@ -8081,16 +8090,16 @@
       <c r="G108" s="14"/>
     </row>
     <row r="109" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D109" s="27"/>
-      <c r="E109" s="27"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="28"/>
       <c r="F109" s="11" t="s">
         <v>517</v>
       </c>
       <c r="G109" s="14"/>
     </row>
     <row r="110" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D110" s="27"/>
-      <c r="E110" s="27"/>
+      <c r="D110" s="28"/>
+      <c r="E110" s="28"/>
       <c r="F110" s="11" t="s">
         <v>518</v>
       </c>
@@ -8109,10 +8118,10 @@
       <c r="G111" s="14"/>
     </row>
     <row r="112" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D112" s="27" t="s">
+      <c r="D112" s="28" t="s">
         <v>521</v>
       </c>
-      <c r="E112" s="27" t="s">
+      <c r="E112" s="28" t="s">
         <v>522</v>
       </c>
       <c r="F112" s="11" t="s">
@@ -8121,44 +8130,44 @@
       <c r="G112" s="14"/>
     </row>
     <row r="113" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D113" s="27"/>
-      <c r="E113" s="27"/>
+      <c r="D113" s="28"/>
+      <c r="E113" s="28"/>
       <c r="F113" s="11" t="s">
         <v>523</v>
       </c>
       <c r="G113" s="14"/>
     </row>
     <row r="114" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D114" s="27"/>
-      <c r="E114" s="27"/>
+      <c r="D114" s="28"/>
+      <c r="E114" s="28"/>
       <c r="F114" s="11" t="s">
         <v>524</v>
       </c>
       <c r="G114" s="14"/>
     </row>
     <row r="115" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D115" s="27" t="s">
+      <c r="D115" s="28" t="s">
         <v>525</v>
       </c>
-      <c r="E115" s="27"/>
+      <c r="E115" s="28"/>
       <c r="F115" s="11" t="s">
         <v>525</v>
       </c>
       <c r="G115" s="14"/>
     </row>
     <row r="116" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D116" s="27"/>
-      <c r="E116" s="27"/>
+      <c r="D116" s="28"/>
+      <c r="E116" s="28"/>
       <c r="F116" s="11" t="s">
         <v>526</v>
       </c>
       <c r="G116" s="14"/>
     </row>
     <row r="117" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D117" s="27" t="s">
+      <c r="D117" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E117" s="27" t="s">
+      <c r="E117" s="28" t="s">
         <v>5</v>
       </c>
       <c r="F117" s="11" t="s">
@@ -8167,18 +8176,18 @@
       <c r="G117" s="14"/>
     </row>
     <row r="118" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D118" s="27"/>
-      <c r="E118" s="27"/>
+      <c r="D118" s="28"/>
+      <c r="E118" s="28"/>
       <c r="F118" s="11" t="s">
         <v>527</v>
       </c>
       <c r="G118" s="14"/>
     </row>
     <row r="119" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D119" s="24" t="s">
+      <c r="D119" s="25" t="s">
         <v>528</v>
       </c>
-      <c r="E119" s="24" t="s">
+      <c r="E119" s="25" t="s">
         <v>529</v>
       </c>
       <c r="F119" s="11" t="s">
@@ -8187,8 +8196,8 @@
       <c r="G119" s="14"/>
     </row>
     <row r="120" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D120" s="25"/>
-      <c r="E120" s="25"/>
+      <c r="D120" s="26"/>
+      <c r="E120" s="26"/>
       <c r="F120" s="11" t="s">
         <v>1158</v>
       </c>
@@ -8277,10 +8286,10 @@
       <c r="G127" s="14"/>
     </row>
     <row r="128" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D128" s="27" t="s">
+      <c r="D128" s="28" t="s">
         <v>541</v>
       </c>
-      <c r="E128" s="27" t="s">
+      <c r="E128" s="28" t="s">
         <v>542</v>
       </c>
       <c r="F128" s="11" t="s">
@@ -8289,18 +8298,18 @@
       <c r="G128" s="14"/>
     </row>
     <row r="129" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D129" s="27"/>
-      <c r="E129" s="27"/>
+      <c r="D129" s="28"/>
+      <c r="E129" s="28"/>
       <c r="F129" s="11" t="s">
         <v>543</v>
       </c>
       <c r="G129" s="14"/>
     </row>
     <row r="130" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D130" s="24" t="s">
+      <c r="D130" s="25" t="s">
         <v>544</v>
       </c>
-      <c r="E130" s="24" t="s">
+      <c r="E130" s="25" t="s">
         <v>545</v>
       </c>
       <c r="F130" s="11" t="s">
@@ -8309,8 +8318,8 @@
       <c r="G130" s="14"/>
     </row>
     <row r="131" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D131" s="25"/>
-      <c r="E131" s="25"/>
+      <c r="D131" s="26"/>
+      <c r="E131" s="26"/>
       <c r="F131" s="11" t="s">
         <v>1206</v>
       </c>
@@ -8341,10 +8350,10 @@
       <c r="G133" s="14"/>
     </row>
     <row r="134" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D134" s="27" t="s">
+      <c r="D134" s="28" t="s">
         <v>550</v>
       </c>
-      <c r="E134" s="27" t="s">
+      <c r="E134" s="28" t="s">
         <v>551</v>
       </c>
       <c r="F134" s="11" t="s">
@@ -8353,8 +8362,8 @@
       <c r="G134" s="14"/>
     </row>
     <row r="135" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D135" s="27"/>
-      <c r="E135" s="27"/>
+      <c r="D135" s="28"/>
+      <c r="E135" s="28"/>
       <c r="F135" s="11" t="s">
         <v>552</v>
       </c>
@@ -8419,10 +8428,10 @@
       <c r="G140" s="14"/>
     </row>
     <row r="141" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D141" s="27" t="s">
+      <c r="D141" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="E141" s="27" t="s">
+      <c r="E141" s="28" t="s">
         <v>563</v>
       </c>
       <c r="F141" s="11" t="s">
@@ -8431,26 +8440,26 @@
       <c r="G141" s="14"/>
     </row>
     <row r="142" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D142" s="27"/>
-      <c r="E142" s="27"/>
+      <c r="D142" s="28"/>
+      <c r="E142" s="28"/>
       <c r="F142" s="11" t="s">
         <v>564</v>
       </c>
       <c r="G142" s="14"/>
     </row>
     <row r="143" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D143" s="27"/>
-      <c r="E143" s="27"/>
+      <c r="D143" s="28"/>
+      <c r="E143" s="28"/>
       <c r="F143" s="11" t="s">
         <v>565</v>
       </c>
       <c r="G143" s="14"/>
     </row>
     <row r="144" spans="4:7" ht="57" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D144" s="27" t="s">
+      <c r="D144" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="E144" s="27" t="s">
+      <c r="E144" s="28" t="s">
         <v>567</v>
       </c>
       <c r="F144" s="11" t="s">
@@ -8459,8 +8468,8 @@
       <c r="G144" s="14"/>
     </row>
     <row r="145" spans="4:7" ht="57" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D145" s="27"/>
-      <c r="E145" s="27"/>
+      <c r="D145" s="28"/>
+      <c r="E145" s="28"/>
       <c r="F145" s="11" t="s">
         <v>568</v>
       </c>
@@ -8571,10 +8580,10 @@
       <c r="G154" s="14"/>
     </row>
     <row r="155" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D155" s="27" t="s">
+      <c r="D155" s="28" t="s">
         <v>585</v>
       </c>
-      <c r="E155" s="27" t="s">
+      <c r="E155" s="28" t="s">
         <v>586</v>
       </c>
       <c r="F155" s="11" t="s">
@@ -8583,26 +8592,26 @@
       <c r="G155" s="14"/>
     </row>
     <row r="156" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D156" s="27"/>
-      <c r="E156" s="27"/>
+      <c r="D156" s="28"/>
+      <c r="E156" s="28"/>
       <c r="F156" s="11" t="s">
         <v>587</v>
       </c>
       <c r="G156" s="14"/>
     </row>
     <row r="157" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D157" s="27"/>
-      <c r="E157" s="27"/>
+      <c r="D157" s="28"/>
+      <c r="E157" s="28"/>
       <c r="F157" s="11" t="s">
         <v>588</v>
       </c>
       <c r="G157" s="14"/>
     </row>
     <row r="158" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D158" s="27" t="s">
+      <c r="D158" s="28" t="s">
         <v>589</v>
       </c>
-      <c r="E158" s="27" t="s">
+      <c r="E158" s="28" t="s">
         <v>590</v>
       </c>
       <c r="F158" s="11" t="s">
@@ -8611,16 +8620,16 @@
       <c r="G158" s="14"/>
     </row>
     <row r="159" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D159" s="27"/>
-      <c r="E159" s="27"/>
+      <c r="D159" s="28"/>
+      <c r="E159" s="28"/>
       <c r="F159" s="11" t="s">
         <v>591</v>
       </c>
       <c r="G159" s="14"/>
     </row>
     <row r="160" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D160" s="27"/>
-      <c r="E160" s="27"/>
+      <c r="D160" s="28"/>
+      <c r="E160" s="28"/>
       <c r="F160" s="11" t="s">
         <v>592</v>
       </c>
@@ -8639,10 +8648,10 @@
       <c r="G161" s="14"/>
     </row>
     <row r="162" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D162" s="24" t="s">
+      <c r="D162" s="25" t="s">
         <v>595</v>
       </c>
-      <c r="E162" s="24" t="s">
+      <c r="E162" s="25" t="s">
         <v>596</v>
       </c>
       <c r="F162" s="11" t="s">
@@ -8651,24 +8660,24 @@
       <c r="G162" s="14"/>
     </row>
     <row r="163" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D163" s="26"/>
-      <c r="E163" s="26"/>
+      <c r="D163" s="27"/>
+      <c r="E163" s="27"/>
       <c r="F163" s="11" t="s">
         <v>597</v>
       </c>
       <c r="G163" s="14"/>
     </row>
     <row r="164" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D164" s="26"/>
-      <c r="E164" s="26"/>
+      <c r="D164" s="27"/>
+      <c r="E164" s="27"/>
       <c r="F164" s="11" t="s">
         <v>598</v>
       </c>
       <c r="G164" s="14"/>
     </row>
     <row r="165" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D165" s="25"/>
-      <c r="E165" s="25"/>
+      <c r="D165" s="26"/>
+      <c r="E165" s="26"/>
       <c r="F165" s="11" t="s">
         <v>1105</v>
       </c>
@@ -8765,10 +8774,10 @@
       <c r="G173" s="14"/>
     </row>
     <row r="174" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D174" s="24" t="s">
+      <c r="D174" s="25" t="s">
         <v>612</v>
       </c>
-      <c r="E174" s="24" t="s">
+      <c r="E174" s="25" t="s">
         <v>613</v>
       </c>
       <c r="F174" s="11" t="s">
@@ -8777,8 +8786,8 @@
       <c r="G174" s="14"/>
     </row>
     <row r="175" spans="4:7" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D175" s="25"/>
-      <c r="E175" s="25"/>
+      <c r="D175" s="26"/>
+      <c r="E175" s="26"/>
       <c r="F175" s="11" t="s">
         <v>614</v>
       </c>
@@ -8821,52 +8830,52 @@
       <c r="G178" s="14"/>
     </row>
     <row r="179" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D179" s="24" t="s">
+      <c r="D179" s="25" t="s">
         <v>621</v>
       </c>
-      <c r="E179" s="24"/>
+      <c r="E179" s="25"/>
       <c r="F179" s="11" t="s">
         <v>621</v>
       </c>
       <c r="G179" s="14"/>
     </row>
     <row r="180" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D180" s="26"/>
-      <c r="E180" s="26"/>
+      <c r="D180" s="27"/>
+      <c r="E180" s="27"/>
       <c r="F180" s="11" t="s">
         <v>622</v>
       </c>
       <c r="G180" s="14"/>
     </row>
     <row r="181" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D181" s="26"/>
-      <c r="E181" s="26"/>
+      <c r="D181" s="27"/>
+      <c r="E181" s="27"/>
       <c r="F181" s="11" t="s">
         <v>623</v>
       </c>
       <c r="G181" s="14"/>
     </row>
     <row r="182" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D182" s="25"/>
-      <c r="E182" s="25"/>
+      <c r="D182" s="26"/>
+      <c r="E182" s="26"/>
       <c r="F182" s="11" t="s">
         <v>624</v>
       </c>
       <c r="G182" s="14"/>
     </row>
     <row r="183" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D183" s="24" t="s">
+      <c r="D183" s="25" t="s">
         <v>625</v>
       </c>
-      <c r="E183" s="24"/>
+      <c r="E183" s="25"/>
       <c r="F183" s="11" t="s">
         <v>625</v>
       </c>
       <c r="G183" s="14"/>
     </row>
     <row r="184" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D184" s="25"/>
-      <c r="E184" s="25"/>
+      <c r="D184" s="26"/>
+      <c r="E184" s="26"/>
       <c r="F184" s="11" t="s">
         <v>626</v>
       </c>
@@ -8885,10 +8894,10 @@
       <c r="G185" s="14"/>
     </row>
     <row r="186" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D186" s="24" t="s">
+      <c r="D186" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="E186" s="24" t="s">
+      <c r="E186" s="25" t="s">
         <v>244</v>
       </c>
       <c r="F186" s="11" t="s">
@@ -8897,8 +8906,8 @@
       <c r="G186" s="14"/>
     </row>
     <row r="187" spans="4:7" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D187" s="25"/>
-      <c r="E187" s="25"/>
+      <c r="D187" s="26"/>
+      <c r="E187" s="26"/>
       <c r="F187" s="11" t="s">
         <v>245</v>
       </c>
@@ -8951,10 +8960,10 @@
       <c r="G191" s="14"/>
     </row>
     <row r="192" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D192" s="24" t="s">
+      <c r="D192" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E192" s="24" t="s">
+      <c r="E192" s="25" t="s">
         <v>43</v>
       </c>
       <c r="F192" s="11" t="s">
@@ -8963,34 +8972,34 @@
       <c r="G192" s="14"/>
     </row>
     <row r="193" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D193" s="25"/>
-      <c r="E193" s="25"/>
+      <c r="D193" s="26"/>
+      <c r="E193" s="26"/>
       <c r="F193" s="11" t="s">
         <v>1093</v>
       </c>
       <c r="G193" s="14"/>
     </row>
     <row r="194" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D194" s="24" t="s">
+      <c r="D194" s="25" t="s">
         <v>636</v>
       </c>
-      <c r="E194" s="24"/>
+      <c r="E194" s="25"/>
       <c r="F194" s="11" t="s">
         <v>636</v>
       </c>
       <c r="G194" s="14"/>
     </row>
     <row r="195" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D195" s="26"/>
-      <c r="E195" s="26"/>
+      <c r="D195" s="27"/>
+      <c r="E195" s="27"/>
       <c r="F195" s="11" t="s">
         <v>637</v>
       </c>
       <c r="G195" s="14"/>
     </row>
     <row r="196" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D196" s="25"/>
-      <c r="E196" s="25"/>
+      <c r="D196" s="26"/>
+      <c r="E196" s="26"/>
       <c r="F196" s="11" t="s">
         <v>638</v>
       </c>
@@ -9105,10 +9114,10 @@
       <c r="G205" s="14"/>
     </row>
     <row r="206" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D206" s="24" t="s">
+      <c r="D206" s="25" t="s">
         <v>657</v>
       </c>
-      <c r="E206" s="24" t="s">
+      <c r="E206" s="25" t="s">
         <v>658</v>
       </c>
       <c r="F206" s="11" t="s">
@@ -9117,8 +9126,8 @@
       <c r="G206" s="14"/>
     </row>
     <row r="207" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D207" s="25"/>
-      <c r="E207" s="25"/>
+      <c r="D207" s="26"/>
+      <c r="E207" s="26"/>
       <c r="F207" s="11" t="s">
         <v>659</v>
       </c>
@@ -9137,10 +9146,10 @@
       <c r="G208" s="14"/>
     </row>
     <row r="209" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D209" s="24" t="s">
+      <c r="D209" s="25" t="s">
         <v>662</v>
       </c>
-      <c r="E209" s="24" t="s">
+      <c r="E209" s="25" t="s">
         <v>663</v>
       </c>
       <c r="F209" s="11" t="s">
@@ -9149,8 +9158,8 @@
       <c r="G209" s="14"/>
     </row>
     <row r="210" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D210" s="25"/>
-      <c r="E210" s="25"/>
+      <c r="D210" s="26"/>
+      <c r="E210" s="26"/>
       <c r="F210" s="11" t="s">
         <v>664</v>
       </c>
@@ -9605,10 +9614,10 @@
       <c r="G248" s="14"/>
     </row>
     <row r="249" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D249" s="24" t="s">
+      <c r="D249" s="25" t="s">
         <v>1069</v>
       </c>
-      <c r="E249" s="24" t="s">
+      <c r="E249" s="25" t="s">
         <v>1070</v>
       </c>
       <c r="F249" s="11" t="s">
@@ -9617,8 +9626,8 @@
       <c r="G249" s="14"/>
     </row>
     <row r="250" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D250" s="25"/>
-      <c r="E250" s="25"/>
+      <c r="D250" s="26"/>
+      <c r="E250" s="26"/>
       <c r="F250" s="11" t="s">
         <v>1165</v>
       </c>
@@ -9725,10 +9734,10 @@
       </c>
     </row>
     <row r="260" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D260" s="20" t="s">
+      <c r="D260" s="21" t="s">
         <v>1150</v>
       </c>
-      <c r="E260" s="20" t="s">
+      <c r="E260" s="21" t="s">
         <v>1151</v>
       </c>
       <c r="F260" s="9" t="s">
@@ -9736,8 +9745,8 @@
       </c>
     </row>
     <row r="261" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D261" s="21"/>
-      <c r="E261" s="21"/>
+      <c r="D261" s="22"/>
+      <c r="E261" s="22"/>
       <c r="F261" s="9" t="s">
         <v>1193</v>
       </c>
@@ -9787,10 +9796,10 @@
       </c>
     </row>
     <row r="266" spans="4:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D266" s="20" t="s">
+      <c r="D266" s="21" t="s">
         <v>1203</v>
       </c>
-      <c r="E266" s="20" t="s">
+      <c r="E266" s="21" t="s">
         <v>1204</v>
       </c>
       <c r="F266" s="10" t="s">
@@ -9798,21 +9807,33 @@
       </c>
     </row>
     <row r="267" spans="4:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D267" s="21"/>
-      <c r="E267" s="21"/>
+      <c r="D267" s="22"/>
+      <c r="E267" s="22"/>
       <c r="F267" s="10" t="s">
         <v>1205</v>
       </c>
     </row>
-    <row r="268" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D268" s="10"/>
-      <c r="E268" s="10"/>
-      <c r="F268" s="9"/>
-    </row>
-    <row r="269" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D269" s="10"/>
-      <c r="E269" s="10"/>
-      <c r="F269" s="9"/>
+    <row r="268" spans="4:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D268" s="10" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E268" s="10" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F268" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="269" spans="4:6" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D269" s="10" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E269" s="10" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F269" s="9" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="270" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D270" s="10"/>
@@ -9823,6 +9844,11 @@
       <c r="D271" s="10"/>
       <c r="E271" s="10"/>
       <c r="F271" s="9"/>
+    </row>
+    <row r="272" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D272" s="10"/>
+      <c r="E272" s="10"/>
+      <c r="F272" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="98">
@@ -9983,10 +10009,10 @@
       <c r="G4" s="14"/>
     </row>
     <row r="5" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="24" t="s">
         <v>254</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -9995,18 +10021,18 @@
       <c r="G5" s="14"/>
     </row>
     <row r="6" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6" s="10" t="s">
         <v>255</v>
       </c>
       <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="21" t="s">
         <v>257</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -10015,18 +10041,18 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="10" t="s">
         <v>1104</v>
       </c>
       <c r="G8" s="14"/>
     </row>
     <row r="9" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>259</v>
       </c>
       <c r="F9" s="10" t="s">
@@ -10035,34 +10061,34 @@
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="2:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="10" t="s">
         <v>260</v>
       </c>
       <c r="G10" s="14"/>
     </row>
     <row r="11" spans="2:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="10" t="s">
         <v>261</v>
       </c>
       <c r="G11" s="14"/>
     </row>
     <row r="12" spans="2:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="10" t="s">
         <v>1163</v>
       </c>
       <c r="G12" s="14"/>
     </row>
     <row r="13" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="24" t="s">
         <v>263</v>
       </c>
       <c r="F13" s="10" t="s">
@@ -10071,18 +10097,18 @@
       <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
       <c r="F14" s="10" t="s">
         <v>265</v>
       </c>
       <c r="G14" s="14"/>
     </row>
     <row r="15" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>267</v>
       </c>
       <c r="F15" s="10" t="s">
@@ -10091,32 +10117,32 @@
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
       <c r="F16" s="10" t="s">
         <v>268</v>
       </c>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="10" t="s">
         <v>269</v>
       </c>
       <c r="G17" s="14"/>
     </row>
     <row r="18" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
       <c r="F18" s="10" t="s">
         <v>1086</v>
       </c>
       <c r="G18" s="14"/>
     </row>
     <row r="19" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
       <c r="F19" s="10" t="s">
         <v>1159</v>
       </c>
@@ -10145,10 +10171,10 @@
       <c r="G21" s="14"/>
     </row>
     <row r="22" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="24" t="s">
         <v>274</v>
       </c>
       <c r="F22" s="10" t="s">
@@ -10157,8 +10183,8 @@
       <c r="G22" s="14"/>
     </row>
     <row r="23" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="10" t="s">
         <v>275</v>
       </c>
@@ -10189,10 +10215,10 @@
       <c r="G25" s="14"/>
     </row>
     <row r="26" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="21" t="s">
         <v>281</v>
       </c>
       <c r="F26" s="10" t="s">
@@ -10201,8 +10227,8 @@
       <c r="G26" s="14"/>
     </row>
     <row r="27" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
       <c r="F27" s="10" t="s">
         <v>1088</v>
       </c>
@@ -10233,18 +10259,18 @@
       <c r="G29" s="14"/>
     </row>
     <row r="30" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="24" t="s">
         <v>286</v>
       </c>
-      <c r="E30" s="23"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="10" t="s">
         <v>286</v>
       </c>
       <c r="G30" s="14"/>
     </row>
     <row r="31" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
       <c r="F31" s="10" t="s">
         <v>287</v>
       </c>
@@ -10287,10 +10313,10 @@
       <c r="G34" s="14"/>
     </row>
     <row r="35" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E35" s="24" t="s">
         <v>295</v>
       </c>
       <c r="F35" s="10" t="s">
@@ -10299,16 +10325,16 @@
       <c r="G35" s="14"/>
     </row>
     <row r="36" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="10" t="s">
         <v>296</v>
       </c>
       <c r="G36" s="14"/>
     </row>
     <row r="37" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
       <c r="F37" s="10" t="s">
         <v>297</v>
       </c>
@@ -10327,44 +10353,44 @@
       <c r="G38" s="14"/>
     </row>
     <row r="39" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="E39" s="20"/>
+      <c r="E39" s="21"/>
       <c r="F39" s="10" t="s">
         <v>300</v>
       </c>
       <c r="G39" s="14"/>
     </row>
     <row r="40" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
       <c r="F40" s="10" t="s">
         <v>301</v>
       </c>
       <c r="G40" s="14"/>
     </row>
     <row r="41" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
       <c r="F41" s="10" t="s">
         <v>302</v>
       </c>
       <c r="G41" s="14"/>
     </row>
     <row r="42" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="10" t="s">
         <v>1115</v>
       </c>
       <c r="G42" s="14"/>
     </row>
     <row r="43" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="E43" s="24" t="s">
         <v>304</v>
       </c>
       <c r="F43" s="10" t="s">
@@ -10373,8 +10399,8 @@
       <c r="G43" s="14"/>
     </row>
     <row r="44" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="10" t="s">
         <v>305</v>
       </c>
@@ -10439,10 +10465,10 @@
       <c r="G49" s="14"/>
     </row>
     <row r="50" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="24" t="s">
         <v>315</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="24" t="s">
         <v>316</v>
       </c>
       <c r="F50" s="10" t="s">
@@ -10451,8 +10477,8 @@
       <c r="G50" s="14"/>
     </row>
     <row r="51" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
       <c r="F51" s="10" t="s">
         <v>317</v>
       </c>
@@ -10531,26 +10557,26 @@
       <c r="G57" s="14"/>
     </row>
     <row r="58" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D58" s="23" t="s">
+      <c r="D58" s="24" t="s">
         <v>330</v>
       </c>
-      <c r="E58" s="23"/>
+      <c r="E58" s="24"/>
       <c r="F58" s="10" t="s">
         <v>330</v>
       </c>
       <c r="G58" s="14"/>
     </row>
     <row r="59" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
       <c r="F59" s="10" t="s">
         <v>331</v>
       </c>
       <c r="G59" s="14"/>
     </row>
     <row r="60" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
       <c r="F60" s="10" t="s">
         <v>1128</v>
       </c>
@@ -10569,10 +10595,10 @@
       <c r="G61" s="14"/>
     </row>
     <row r="62" spans="4:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="21" t="s">
         <v>335</v>
       </c>
       <c r="F62" s="10" t="s">
@@ -10581,8 +10607,8 @@
       <c r="G62" s="14"/>
     </row>
     <row r="63" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
       <c r="F63" s="10" t="s">
         <v>1161</v>
       </c>
@@ -10601,10 +10627,10 @@
       <c r="G64" s="14"/>
     </row>
     <row r="65" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D65" s="20" t="s">
+      <c r="D65" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="21" t="s">
         <v>339</v>
       </c>
       <c r="F65" s="10" t="s">
@@ -10613,8 +10639,8 @@
       <c r="G65" s="14"/>
     </row>
     <row r="66" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
       <c r="F66" s="10" t="s">
         <v>1164</v>
       </c>
@@ -10643,10 +10669,10 @@
       <c r="G68" s="14"/>
     </row>
     <row r="69" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="24" t="s">
         <v>343</v>
       </c>
-      <c r="E69" s="23" t="s">
+      <c r="E69" s="24" t="s">
         <v>344</v>
       </c>
       <c r="F69" s="10" t="s">
@@ -10655,18 +10681,18 @@
       <c r="G69" s="14"/>
     </row>
     <row r="70" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
       <c r="F70" s="10" t="s">
         <v>345</v>
       </c>
       <c r="G70" s="14"/>
     </row>
     <row r="71" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="23" t="s">
+      <c r="D71" s="24" t="s">
         <v>346</v>
       </c>
-      <c r="E71" s="23" t="s">
+      <c r="E71" s="24" t="s">
         <v>347</v>
       </c>
       <c r="F71" s="10" t="s">
@@ -10675,8 +10701,8 @@
       <c r="G71" s="14"/>
     </row>
     <row r="72" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
       <c r="F72" s="10" t="s">
         <v>348</v>
       </c>
@@ -10719,10 +10745,10 @@
       <c r="G75" s="14"/>
     </row>
     <row r="76" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="24" t="s">
         <v>358</v>
       </c>
-      <c r="E76" s="23" t="s">
+      <c r="E76" s="24" t="s">
         <v>359</v>
       </c>
       <c r="F76" s="10" t="s">
@@ -10731,8 +10757,8 @@
       <c r="G76" s="14"/>
     </row>
     <row r="77" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D77" s="23"/>
-      <c r="E77" s="23"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
       <c r="F77" s="10" t="s">
         <v>360</v>
       </c>
@@ -11048,10 +11074,10 @@
       <c r="G3" s="15"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="21" t="s">
         <v>104</v>
       </c>
       <c r="F4" s="10" t="s">
@@ -11060,8 +11086,8 @@
       <c r="G4" s="14"/>
     </row>
     <row r="5" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
       <c r="F5" s="10" t="s">
         <v>105</v>
       </c>
@@ -11090,10 +11116,10 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>110</v>
       </c>
       <c r="F8" s="10" t="s">
@@ -11102,8 +11128,8 @@
       <c r="G8" s="14"/>
     </row>
     <row r="9" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="10" t="s">
         <v>1089</v>
       </c>
@@ -11122,10 +11148,10 @@
       <c r="G10" s="14"/>
     </row>
     <row r="11" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="10" t="s">
@@ -11137,8 +11163,8 @@
       <c r="J11"/>
     </row>
     <row r="12" spans="2:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="10" t="s">
         <v>115</v>
       </c>
@@ -11206,10 +11232,10 @@
       <c r="J16"/>
     </row>
     <row r="17" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="21" t="s">
         <v>124</v>
       </c>
       <c r="F17" s="10" t="s">
@@ -11221,8 +11247,8 @@
       <c r="J17"/>
     </row>
     <row r="18" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
       <c r="F18" s="10" t="s">
         <v>125</v>
       </c>
@@ -11247,10 +11273,10 @@
       <c r="J19"/>
     </row>
     <row r="20" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="21" t="s">
         <v>129</v>
       </c>
       <c r="F20" s="10" t="s">
@@ -11262,8 +11288,8 @@
       <c r="J20"/>
     </row>
     <row r="21" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
       <c r="F21" s="10" t="s">
         <v>130</v>
       </c>
@@ -11316,10 +11342,10 @@
       <c r="J24"/>
     </row>
     <row r="25" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="21" t="s">
         <v>137</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -11331,8 +11357,8 @@
       <c r="J25"/>
     </row>
     <row r="26" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
       <c r="F26" s="10" t="s">
         <v>138</v>
       </c>
@@ -11357,10 +11383,10 @@
       <c r="J27"/>
     </row>
     <row r="28" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="21" t="s">
         <v>141</v>
       </c>
       <c r="F28" s="10" t="s">
@@ -11372,8 +11398,8 @@
       <c r="J28"/>
     </row>
     <row r="29" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
       <c r="F29" s="10" t="s">
         <v>143</v>
       </c>
@@ -11454,10 +11480,10 @@
       <c r="J34"/>
     </row>
     <row r="35" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="21" t="s">
         <v>153</v>
       </c>
       <c r="F35" s="10" t="s">
@@ -11469,8 +11495,8 @@
       <c r="J35"/>
     </row>
     <row r="36" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
       <c r="F36" s="10" t="s">
         <v>154</v>
       </c>
@@ -11480,10 +11506,10 @@
       <c r="J36"/>
     </row>
     <row r="37" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="E37" s="20"/>
+      <c r="E37" s="21"/>
       <c r="F37" s="10" t="s">
         <v>155</v>
       </c>
@@ -11493,8 +11519,8 @@
       <c r="J37"/>
     </row>
     <row r="38" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
       <c r="F38" s="10" t="s">
         <v>156</v>
       </c>
@@ -11519,10 +11545,10 @@
       <c r="J39"/>
     </row>
     <row r="40" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="21" t="s">
         <v>160</v>
       </c>
       <c r="F40" s="10" t="s">
@@ -11534,8 +11560,8 @@
       <c r="J40"/>
     </row>
     <row r="41" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
       <c r="F41" s="10" t="s">
         <v>161</v>
       </c>
@@ -11545,8 +11571,8 @@
       <c r="J41"/>
     </row>
     <row r="42" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="10" t="s">
         <v>162</v>
       </c>
@@ -11556,10 +11582,10 @@
       <c r="J42"/>
     </row>
     <row r="43" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="21" t="s">
         <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
@@ -11571,8 +11597,8 @@
       <c r="J43"/>
     </row>
     <row r="44" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
       <c r="F44" s="10" t="s">
         <v>165</v>
       </c>
@@ -11743,10 +11769,10 @@
       <c r="J55"/>
     </row>
     <row r="56" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D56" s="20" t="s">
+      <c r="D56" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="E56" s="20"/>
+      <c r="E56" s="21"/>
       <c r="F56" s="10" t="s">
         <v>64</v>
       </c>
@@ -11756,8 +11782,8 @@
       <c r="J56"/>
     </row>
     <row r="57" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="10" t="s">
         <v>1095</v>
       </c>
@@ -11767,10 +11793,10 @@
       <c r="J57"/>
     </row>
     <row r="58" spans="4:10" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="21" t="s">
         <v>188</v>
       </c>
       <c r="F58" s="10" t="s">
@@ -11782,8 +11808,8 @@
       <c r="J58"/>
     </row>
     <row r="59" spans="4:10" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
       <c r="F59" s="10" t="s">
         <v>190</v>
       </c>
@@ -11793,8 +11819,8 @@
       <c r="J59"/>
     </row>
     <row r="60" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
       <c r="F60" s="10" t="s">
         <v>191</v>
       </c>
@@ -11849,10 +11875,10 @@
       <c r="J63"/>
     </row>
     <row r="64" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D64" s="20" t="s">
+      <c r="D64" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="21" t="s">
         <v>199</v>
       </c>
       <c r="F64" s="10" t="s">
@@ -11864,8 +11890,8 @@
       <c r="J64"/>
     </row>
     <row r="65" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
       <c r="F65" s="10" t="s">
         <v>200</v>
       </c>
@@ -11875,8 +11901,8 @@
       <c r="J65"/>
     </row>
     <row r="66" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
       <c r="F66" s="10" t="s">
         <v>201</v>
       </c>
@@ -11961,10 +11987,10 @@
       <c r="J71"/>
     </row>
     <row r="72" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="20" t="s">
+      <c r="D72" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="E72" s="21" t="s">
         <v>212</v>
       </c>
       <c r="F72" s="10" t="s">
@@ -11976,8 +12002,8 @@
       <c r="J72"/>
     </row>
     <row r="73" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
       <c r="F73" s="10" t="s">
         <v>213</v>
       </c>
@@ -12000,10 +12026,10 @@
       <c r="J74"/>
     </row>
     <row r="75" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D75" s="20" t="s">
+      <c r="D75" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="E75" s="20"/>
+      <c r="E75" s="21"/>
       <c r="F75" s="10" t="s">
         <v>215</v>
       </c>
@@ -12013,8 +12039,8 @@
       <c r="J75"/>
     </row>
     <row r="76" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D76" s="22"/>
-      <c r="E76" s="22"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
       <c r="F76" s="10" t="s">
         <v>216</v>
       </c>
@@ -12024,8 +12050,8 @@
       <c r="J76"/>
     </row>
     <row r="77" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
       <c r="F77" s="10" t="s">
         <v>217</v>
       </c>
@@ -12095,10 +12121,10 @@
       <c r="J81"/>
     </row>
     <row r="82" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D82" s="20" t="s">
+      <c r="D82" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="E82" s="20" t="s">
+      <c r="E82" s="21" t="s">
         <v>227</v>
       </c>
       <c r="F82" s="10" t="s">
@@ -12110,8 +12136,8 @@
       <c r="J82"/>
     </row>
     <row r="83" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
       <c r="F83" s="10" t="s">
         <v>228</v>
       </c>
@@ -12136,10 +12162,10 @@
       <c r="J84"/>
     </row>
     <row r="85" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D85" s="20" t="s">
+      <c r="D85" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E85" s="20" t="s">
+      <c r="E85" s="21" t="s">
         <v>47</v>
       </c>
       <c r="F85" s="10" t="s">
@@ -12151,8 +12177,8 @@
       <c r="J85"/>
     </row>
     <row r="86" spans="4:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D86" s="22"/>
-      <c r="E86" s="22"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
       <c r="F86" s="10" t="s">
         <v>232</v>
       </c>
@@ -12162,8 +12188,8 @@
       <c r="J86"/>
     </row>
     <row r="87" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D87" s="21"/>
-      <c r="E87" s="21"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
       <c r="F87" s="10" t="s">
         <v>233</v>
       </c>
@@ -12246,10 +12272,10 @@
       <c r="J92"/>
     </row>
     <row r="93" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D93" s="20" t="s">
+      <c r="D93" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="E93" s="20" t="s">
+      <c r="E93" s="21" t="s">
         <v>244</v>
       </c>
       <c r="F93" s="10" t="s">
@@ -12261,8 +12287,8 @@
       <c r="J93"/>
     </row>
     <row r="94" spans="4:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D94" s="21"/>
-      <c r="E94" s="21"/>
+      <c r="D94" s="22"/>
+      <c r="E94" s="22"/>
       <c r="F94" s="10" t="s">
         <v>245</v>
       </c>
@@ -12473,10 +12499,10 @@
       <c r="G4" s="15"/>
     </row>
     <row r="5" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="24" t="s">
         <v>100</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -12485,18 +12511,18 @@
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6" s="10" t="s">
         <v>101</v>
       </c>
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -12505,26 +12531,26 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="2:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="10" t="s">
         <v>54</v>
       </c>
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="2:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="10" t="s">
         <v>55</v>
       </c>
       <c r="G9" s="15"/>
     </row>
     <row r="10" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="24" t="s">
         <v>57</v>
       </c>
       <c r="F10" s="10" t="s">
@@ -12533,18 +12559,18 @@
       <c r="G10" s="15"/>
     </row>
     <row r="11" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="10" t="s">
         <v>58</v>
       </c>
       <c r="G11" s="15"/>
     </row>
     <row r="12" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="24" t="s">
         <v>60</v>
       </c>
       <c r="F12" s="10" t="s">
@@ -12553,8 +12579,8 @@
       <c r="G12" s="15"/>
     </row>
     <row r="13" spans="2:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="10" t="s">
         <v>62</v>
       </c>
@@ -12593,10 +12619,10 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="21" t="s">
         <v>69</v>
       </c>
       <c r="F17" s="10" t="s">
@@ -12605,8 +12631,8 @@
       <c r="G17" s="15"/>
     </row>
     <row r="18" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
       <c r="F18" s="10" t="s">
         <v>1108</v>
       </c>
@@ -12625,10 +12651,10 @@
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="24" t="s">
         <v>73</v>
       </c>
       <c r="F20" s="10" t="s">
@@ -12637,18 +12663,18 @@
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
       <c r="F21" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="24" t="s">
         <v>76</v>
       </c>
       <c r="F22" s="10" t="s">
@@ -12657,8 +12683,8 @@
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="4:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="10" t="s">
         <v>78</v>
       </c>
@@ -12815,10 +12841,10 @@
       </c>
     </row>
     <row r="37" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>356</v>
       </c>
       <c r="F37" s="10" t="s">
@@ -12826,15 +12852,15 @@
       </c>
     </row>
     <row r="38" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
       <c r="F38" s="10" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="39" spans="4:7" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
       <c r="F39" s="10" t="s">
         <v>1176</v>
       </c>
@@ -12942,10 +12968,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="10" t="str">
-        <f t="shared" ref="H3:H6" si="0">E3 &amp; " (" &amp; F3 &amp; ")"</f>
+        <f t="shared" ref="H3:H5" si="0">E3 &amp; " (" &amp; F3 &amp; ")"</f>
         <v>Dark Summoner to Dekiteiru (I'm Dating a Dark Summoner)</v>
       </c>
-      <c r="I3" s="28"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10"/>
@@ -12966,7 +12992,7 @@
         <f t="shared" si="0"/>
         <v>Kanojo no Tomodachi (My Girlfriend's Friend)</v>
       </c>
-      <c r="I4" s="28"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="2:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
@@ -12987,7 +13013,7 @@
         <f t="shared" si="0"/>
         <v>Hyouken no Majutsushi ga Sekai wo Suberu (The Iceblade Sorcerer Shall Rule the World)</v>
       </c>
-      <c r="I5" s="28"/>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="2:12" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="10"/>
@@ -13005,10 +13031,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f>E6 &amp; " (" &amp; F6 &amp; ")"</f>
         <v>Mouse Cursor de Genjitsu wo Sousa Dekiru You ni Natta node, Onna no Ko wo Ippai Click Shimaasu (Now That I Can Control Reality with a Mouse Cursor, I'm Gonna Click Away on the Girls!)</v>
       </c>
-      <c r="I6" s="28"/>
+      <c r="I6" s="12"/>
     </row>
     <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="10"/>
@@ -13027,33 +13053,49 @@
         <f t="shared" ref="H7:H12" si="1">E7 &amp; " (" &amp; F7 &amp; ")"</f>
         <v xml:space="preserve"> (Magical Explorer)</v>
       </c>
-      <c r="I7" s="28"/>
-    </row>
-    <row r="8" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="2:12" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="C8" s="10" t="b">
+        <v>1</v>
+      </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
       <c r="H8" s="10" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> ()</v>
-      </c>
-      <c r="I8" s="28"/>
-    </row>
-    <row r="9" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>Shinja Zero no Megami-sama to Hajimeru Isekai Kouryaku (Full Clearing Another World under a Goddess with Zero Believers)</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="2:12" ht="132" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="C9" s="10" t="b">
+        <v>1</v>
+      </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
       <c r="H9" s="10" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> ()</v>
-      </c>
-      <c r="I9" s="28"/>
+        <v>Tsuihou sareta Cheat Fuyo Majutsushi wa Kimama na Second Life wo Ouka suru. Ore wa Buki dake ja Naku, Arayuru Mono ni "Kyouka Point" wo Fuyo Dekiru shi, Ore no Ishi de Itsudemo Kouka wo Kaijo Dekiru kedo, Nokotta Hitotachi Daijoubu? (The Laid-Off Cheat-Granting Mage Enjoys a Second Lease on Life)</v>
+      </c>
+      <c r="I9" s="12"/>
     </row>
     <row r="10" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="10"/>
@@ -13066,7 +13108,7 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> ()</v>
       </c>
-      <c r="I10" s="28"/>
+      <c r="I10" s="12"/>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="10"/>
@@ -13079,7 +13121,7 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> ()</v>
       </c>
-      <c r="I11" s="28"/>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="10"/>
@@ -13092,7 +13134,7 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> ()</v>
       </c>
-      <c r="I12" s="28"/>
+      <c r="I12" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13154,7 +13196,7 @@
       <c r="F3" s="10">
         <v>3</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="12" t="s">
         <v>1135</v>
       </c>
       <c r="H3" s="12"/>
@@ -13173,7 +13215,7 @@
       <c r="F4" s="10">
         <v>2</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="12" t="s">
         <v>1092</v>
       </c>
       <c r="H4" s="12"/>
@@ -13194,7 +13236,7 @@
       <c r="F5" s="10">
         <v>3</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="12" t="s">
         <v>1170</v>
       </c>
       <c r="H5" s="12"/>
@@ -13215,7 +13257,7 @@
       <c r="F6" s="10">
         <v>2</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="12" t="s">
         <v>1194</v>
       </c>
       <c r="H6" s="12"/>
@@ -13236,7 +13278,7 @@
       <c r="F7" s="10">
         <v>1</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="12" t="s">
         <v>1198</v>
       </c>
       <c r="H7" s="12"/>
@@ -13257,7 +13299,7 @@
       <c r="F8" s="10">
         <v>2</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="12" t="s">
         <v>1211</v>
       </c>
       <c r="H8" s="12"/>
@@ -13268,7 +13310,7 @@
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="28"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13277,7 +13319,7 @@
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="28"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13286,7 +13328,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="28"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13295,7 +13337,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
-      <c r="G12" s="28"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13304,7 +13346,7 @@
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="28"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13313,7 +13355,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="28"/>
+      <c r="G14" s="12"/>
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13322,7 +13364,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="28"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13331,7 +13373,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="28"/>
+      <c r="G16" s="12"/>
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13340,7 +13382,7 @@
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="28"/>
+      <c r="G17" s="12"/>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13349,7 +13391,7 @@
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
-      <c r="G18" s="28"/>
+      <c r="G18" s="12"/>
       <c r="H18" s="12"/>
     </row>
   </sheetData>
@@ -13388,7 +13430,7 @@
       <c r="E3" s="10" t="s">
         <v>1201</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="12" t="s">
         <v>1202</v>
       </c>
     </row>
@@ -13397,7 +13439,7 @@
         <v>1096</v>
       </c>
       <c r="E4" s="10"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="12" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -13408,7 +13450,7 @@
       <c r="E5" s="10" t="s">
         <v>1100</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="12" t="s">
         <v>1098</v>
       </c>
     </row>
@@ -13417,7 +13459,7 @@
         <v>1101</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="12" t="s">
         <v>1102</v>
       </c>
     </row>
@@ -13426,7 +13468,7 @@
         <v>1106</v>
       </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="12" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -13435,49 +13477,49 @@
         <v>1146</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="12" t="s">
         <v>1147</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="28"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="28"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="28"/>
+      <c r="F11" s="12"/>
     </row>
     <row r="12" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="28"/>
+      <c r="F12" s="12"/>
     </row>
     <row r="13" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="28"/>
+      <c r="F13" s="12"/>
     </row>
     <row r="14" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
-      <c r="F14" s="28"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="28"/>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="4:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="28"/>
+      <c r="F16" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
